--- a/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262415</t>
+          <t>263171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272104</t>
+          <t>272115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251657</t>
+          <t>251984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259788</t>
+          <t>259793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519227</t>
+          <t>518702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531096</t>
+          <t>531307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471824</t>
+          <t>472119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487079</t>
+          <t>487046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488207</t>
+          <t>488883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499883</t>
+          <t>500012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966691</t>
+          <t>965977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984922</t>
+          <t>985016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313267</t>
+          <t>313258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331009</t>
+          <t>329346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647324</t>
+          <t>647519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342417</t>
+          <t>342162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354235</t>
+          <t>354492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360669</t>
+          <t>360483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369613</t>
+          <t>369644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708319</t>
+          <t>708280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722868</t>
+          <t>722561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190515</t>
+          <t>190801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200599</t>
+          <t>200668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188596</t>
+          <t>188908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202379</t>
+          <t>202467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384740</t>
+          <t>384696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400225</t>
+          <t>400770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265739</t>
+          <t>264862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273357</t>
+          <t>273153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541898</t>
+          <t>542048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595705</t>
+          <t>596427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609747</t>
+          <t>609923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>617945</t>
+          <t>619253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632207</t>
+          <t>632326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1219578</t>
+          <t>1221004</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1239372</t>
+          <t>1239516</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35448</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728518</t>
+          <t>727706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>739794</t>
+          <t>739823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>757643</t>
+          <t>756673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>774263</t>
+          <t>773958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1491858</t>
+          <t>1491621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>66661</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73473</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86200</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>127417</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3210284</t>
+          <t>3209882</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3238540</t>
+          <t>3238882</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3305724</t>
+          <t>3306750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3336464</t>
+          <t>3336061</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6528237</t>
+          <t>6528324</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6569541</t>
+          <t>6567927</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275831</t>
+          <t>274466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290049</t>
+          <t>289135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268319</t>
+          <t>268450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282296</t>
+          <t>282168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549289</t>
+          <t>550326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569201</t>
+          <t>569532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489014</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502506</t>
+          <t>502466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506200</t>
+          <t>506407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518755</t>
+          <t>518742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000448</t>
+          <t>1002496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018906</t>
+          <t>1019049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309605</t>
+          <t>308883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322003</t>
+          <t>322049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331196</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340038</t>
+          <t>340033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646350</t>
+          <t>646765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660112</t>
+          <t>660234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364087</t>
+          <t>364772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372897</t>
+          <t>372913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366557</t>
+          <t>367105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382221</t>
+          <t>382302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736712</t>
+          <t>737648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753742</t>
+          <t>753889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187323</t>
+          <t>187747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204649</t>
+          <t>204168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196905</t>
+          <t>197736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212760</t>
+          <t>212745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390715</t>
+          <t>392670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413264</t>
+          <t>413804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268565</t>
+          <t>267700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271820</t>
+          <t>271577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279088</t>
+          <t>279082</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544587</t>
+          <t>543844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552972</t>
+          <t>552960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32401</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648483</t>
+          <t>649291</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659799</t>
+          <t>659875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671393</t>
+          <t>670868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686566</t>
+          <t>686651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324240</t>
+          <t>1325749</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344012</t>
+          <t>1344066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>29937</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764331</t>
+          <t>764943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775909</t>
+          <t>775972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>803459</t>
+          <t>802988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817394</t>
+          <t>817444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1573017</t>
+          <t>1573014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590217</t>
+          <t>1591206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43387</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>76525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,34 +6820,34 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>77898</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>62695</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>97628</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>77898</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>98308</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>113441</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>161895</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3351735</t>
+          <t>3350254</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3383392</t>
+          <t>3383325</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,42 +6928,42 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3480411</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3460681</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3495614</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3480411</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3460001</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3495632</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6823193</t>
+          <t>6824507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6872617</t>
+          <t>6871647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286022</t>
+          <t>285275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>277598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286638</t>
+          <t>286783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567800</t>
+          <t>567377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579270</t>
+          <t>578689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495865</t>
+          <t>495245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515584</t>
+          <t>516482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016037</t>
+          <t>1016339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024646</t>
+          <t>1024667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310684</t>
+          <t>311369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330853</t>
+          <t>330012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645840</t>
+          <t>645671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653977</t>
+          <t>653982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358489</t>
+          <t>357917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369066</t>
+          <t>369060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370839</t>
+          <t>369159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383907</t>
+          <t>383815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>734239</t>
+          <t>734522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>751055</t>
+          <t>750838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,62 +8786,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1746</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205691</t>
+          <t>204891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>423929</t>
+          <t>424427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248917</t>
+          <t>248624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260532</t>
+          <t>260971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264148</t>
+          <t>264545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272107</t>
+          <t>272155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517894</t>
+          <t>517279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530882</t>
+          <t>531339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637854</t>
+          <t>638664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652260</t>
+          <t>652314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674869</t>
+          <t>674206</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686888</t>
+          <t>687741</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318145</t>
+          <t>1318266</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1336894</t>
+          <t>1337904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763849</t>
+          <t>764026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775884</t>
+          <t>775865</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812530</t>
+          <t>812505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823664</t>
+          <t>823469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580477</t>
+          <t>1581287</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597672</t>
+          <t>1597594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>93225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3344341</t>
+          <t>3345542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3370934</t>
+          <t>3371354</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3492526</t>
+          <t>3493213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3517270</t>
+          <t>3517996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6847936</t>
+          <t>6845667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6884259</t>
+          <t>6882857</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301621</t>
+          <t>302405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280518</t>
+          <t>280333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287291</t>
+          <t>287283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585812</t>
+          <t>586787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597099</t>
+          <t>597157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38521</t>
+          <t>39163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480078</t>
+          <t>480355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501317</t>
+          <t>501095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476448</t>
+          <t>475806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493171</t>
+          <t>492717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>963862</t>
+          <t>962798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990268</t>
+          <t>990646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301959</t>
+          <t>302492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312553</t>
+          <t>312798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>339939</t>
+          <t>340186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346852</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646592</t>
+          <t>645149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657895</t>
+          <t>658020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>295188</t>
+          <t>293990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309679</t>
+          <t>309120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458466</t>
+          <t>455827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472547</t>
+          <t>472822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>759875</t>
+          <t>760212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>780467</t>
+          <t>779962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174175</t>
+          <t>174580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249335</t>
+          <t>249776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256428</t>
+          <t>256454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426674</t>
+          <t>426825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434032</t>
+          <t>434122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256883</t>
+          <t>255355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265842</t>
+          <t>265581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240432</t>
+          <t>240250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250198</t>
+          <t>250386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499682</t>
+          <t>500214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514496</t>
+          <t>514148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34415</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>510427</t>
+          <t>542535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61164</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>732909</t>
+          <t>690933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589864</t>
+          <t>591364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610031</t>
+          <t>610768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338838</t>
+          <t>306730</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>805916</t>
+          <t>806738</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>740635</t>
+          <t>782611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1412380</t>
+          <t>1413560</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>920051</t>
+          <t>918871</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928338</t>
+          <t>928298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>708808</t>
+          <t>708909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>715635</t>
+          <t>715593</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1631560</t>
+          <t>1632510</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1642485</t>
+          <t>1642970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>58510</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>99242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>941132</t>
+          <t>935404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176341</t>
+          <t>177115</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1103892</t>
+          <t>1053611</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3364229</t>
+          <t>3360575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3403399</t>
+          <t>3401307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2771148</t>
+          <t>2776876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3608767</t>
+          <t>3608752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6068205</t>
+          <t>6118486</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6995756</t>
+          <t>6994982</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263171</t>
+          <t>263035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272115</t>
+          <t>272108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251984</t>
+          <t>251969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259793</t>
+          <t>259782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518702</t>
+          <t>518069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531307</t>
+          <t>531127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31047</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472119</t>
+          <t>473280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487046</t>
+          <t>487137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488883</t>
+          <t>488344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500012</t>
+          <t>500018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965977</t>
+          <t>965714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985016</t>
+          <t>985111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>313268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329346</t>
+          <t>330778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647519</t>
+          <t>647856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>342242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354492</t>
+          <t>354487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360483</t>
+          <t>360789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369644</t>
+          <t>369623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708280</t>
+          <t>707498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722561</t>
+          <t>722587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190801</t>
+          <t>191441</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200668</t>
+          <t>200680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188908</t>
+          <t>188626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202467</t>
+          <t>202273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384696</t>
+          <t>385502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400770</t>
+          <t>401138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264862</t>
+          <t>266688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273153</t>
+          <t>272423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542048</t>
+          <t>542964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>32149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596427</t>
+          <t>596218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609923</t>
+          <t>609728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619253</t>
+          <t>618686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632326</t>
+          <t>632348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1221004</t>
+          <t>1221097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1239516</t>
+          <t>1239842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>36662</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>727706</t>
+          <t>727445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>739823</t>
+          <t>739904</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756673</t>
+          <t>757589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773958</t>
+          <t>774289</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1491621</t>
+          <t>1490644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1511398</t>
+          <t>1512100</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66661</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3209882</t>
+          <t>3210937</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3238882</t>
+          <t>3238841</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3306750</t>
+          <t>3305655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3336061</t>
+          <t>3336142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6528324</t>
+          <t>6527907</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6567927</t>
+          <t>6567956</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274466</t>
+          <t>275830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289135</t>
+          <t>289099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268450</t>
+          <t>268271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282168</t>
+          <t>281823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550326</t>
+          <t>549943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569532</t>
+          <t>569621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489060</t>
+          <t>489278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502466</t>
+          <t>502482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506407</t>
+          <t>505404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518742</t>
+          <t>518656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002496</t>
+          <t>1001702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019049</t>
+          <t>1018892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308883</t>
+          <t>308549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322049</t>
+          <t>322035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340033</t>
+          <t>340042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646765</t>
+          <t>645784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660234</t>
+          <t>660070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364772</t>
+          <t>364838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372913</t>
+          <t>372900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367105</t>
+          <t>367832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382302</t>
+          <t>383030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737648</t>
+          <t>737071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753889</t>
+          <t>754347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187747</t>
+          <t>188012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204168</t>
+          <t>204538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197736</t>
+          <t>198342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212745</t>
+          <t>213477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392670</t>
+          <t>392754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413804</t>
+          <t>413330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267700</t>
+          <t>269605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271577</t>
+          <t>271692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279082</t>
+          <t>279095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543844</t>
+          <t>543684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552960</t>
+          <t>552954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649291</t>
+          <t>647546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659875</t>
+          <t>659612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670868</t>
+          <t>670841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686651</t>
+          <t>686638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325749</t>
+          <t>1324494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344066</t>
+          <t>1344374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,77 +6477,77 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>19724</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>19254</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>10702</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>29107</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>6409</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>20865</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>19254</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>11745</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>29937</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764943</t>
+          <t>765346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775972</t>
+          <t>776005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,82 +6585,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>811942</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>804129</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>817622</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1583697</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1573844</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1592249</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,18%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>811942</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>802988</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>817444</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1583697</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1573014</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1591206</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76525</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97628</t>
+          <t>96951</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160581</t>
+          <t>162776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350254</t>
+          <t>3351489</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3383325</t>
+          <t>3384107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3460681</t>
+          <t>3461358</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3495614</t>
+          <t>3497036</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6824507</t>
+          <t>6822312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6871647</t>
+          <t>6873063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285275</t>
+          <t>286282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277598</t>
+          <t>277268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286783</t>
+          <t>286769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567377</t>
+          <t>567192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578689</t>
+          <t>578728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,44 +7742,44 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495245</t>
+          <t>495565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,49 +7850,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>520931</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>515426</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>523084</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>520931</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>516482</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>523084</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>955</t>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016339</t>
+          <t>1015334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024667</t>
+          <t>1024498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311369</t>
+          <t>310721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330012</t>
+          <t>330007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645671</t>
+          <t>645293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653982</t>
+          <t>653977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>22554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357917</t>
+          <t>359194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369060</t>
+          <t>369064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369159</t>
+          <t>368206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383815</t>
+          <t>383185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>734522</t>
+          <t>734693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750838</t>
+          <t>751098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204891</t>
+          <t>205356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424427</t>
+          <t>423625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>249553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260971</t>
+          <t>260213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264545</t>
+          <t>263046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272155</t>
+          <t>272105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517279</t>
+          <t>517461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531339</t>
+          <t>531305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638664</t>
+          <t>637897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652314</t>
+          <t>652364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674206</t>
+          <t>674270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687741</t>
+          <t>687109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318266</t>
+          <t>1317839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337904</t>
+          <t>1337292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764026</t>
+          <t>762983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775865</t>
+          <t>775867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812505</t>
+          <t>812726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823469</t>
+          <t>823696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581287</t>
+          <t>1581778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597594</t>
+          <t>1597517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,49 +10138,49 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>37722</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>26305</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>51035</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>37722</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>26546</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>51329</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93225</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3345542</t>
+          <t>3344239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371354</t>
+          <t>3371446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,47 +10251,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3506820</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3493507</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3518237</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3506820</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3493213</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3517996</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6845667</t>
+          <t>6848283</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6882857</t>
+          <t>6884511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308888</t>
+          <t>316746</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302405</t>
+          <t>311809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284654</t>
+          <t>310541</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280333</t>
+          <t>306410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287283</t>
+          <t>313331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>593541</t>
+          <t>627287</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586787</t>
+          <t>620496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597157</t>
+          <t>630519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25608</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38035</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39163</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>57509</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>72558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>492782</t>
+          <t>504642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480355</t>
+          <t>492650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501095</t>
+          <t>514247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>485513</t>
+          <t>514990</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475806</t>
+          <t>505060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492717</t>
+          <t>522995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>978295</t>
+          <t>1019632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>962798</t>
+          <t>1004583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990646</t>
+          <t>1031919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,27 +11383,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>19471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11496,22 +11496,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308680</t>
+          <t>308780</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302492</t>
+          <t>302428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312798</t>
+          <t>312371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>344282</t>
+          <t>351554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340186</t>
+          <t>347586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346941</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>652962</t>
+          <t>660335</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645149</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658020</t>
+          <t>665037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304882</t>
+          <t>364668</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293990</t>
+          <t>355149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309120</t>
+          <t>369993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>468346</t>
+          <t>413976</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455827</t>
+          <t>401927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472822</t>
+          <t>418226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>773227</t>
+          <t>778645</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>760212</t>
+          <t>764135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>779962</t>
+          <t>786318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -12182,22 +12182,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177565</t>
+          <t>204412</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174580</t>
+          <t>200865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>253527</t>
+          <t>223245</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249776</t>
+          <t>219417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256454</t>
+          <t>225746</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>431092</t>
+          <t>427656</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426825</t>
+          <t>423565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434122</t>
+          <t>430712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262234</t>
+          <t>262760</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255355</t>
+          <t>257011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265581</t>
+          <t>266738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>246309</t>
+          <t>252949</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240250</t>
+          <t>247253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250386</t>
+          <t>257233</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>508543</t>
+          <t>515709</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500214</t>
+          <t>507835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514148</t>
+          <t>521824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>44718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>240185</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>542535</t>
+          <t>62138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>261934</t>
+          <t>78452</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>62064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>690933</t>
+          <t>96920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>602529</t>
+          <t>689850</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591364</t>
+          <t>674969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610768</t>
+          <t>699885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>609080</t>
+          <t>723443</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>306730</t>
+          <t>709919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>806738</t>
+          <t>733954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1211610</t>
+          <t>1413292</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>782611</t>
+          <t>1394824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1413560</t>
+          <t>1429680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,67 +13133,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>10935</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>5872</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>19981</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>7833</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3482</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>13942</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>925502</t>
+          <t>792898</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>918871</t>
+          <t>785454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928298</t>
+          <t>796878</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,67 +13246,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>713115</t>
+          <t>825570</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>708909</t>
+          <t>820857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>715593</t>
+          <t>828736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1618468</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1609422</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1623531</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1811</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1638619</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1632510</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1642970</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,102 +13441,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58510</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99242</t>
+          <t>110224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>120685</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>102653</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>141561</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>208690</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>185026</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>238607</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>307454</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>103528</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>935404</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>384209</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>177115</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>1053611</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -13554,102 +13554,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3383062</t>
+          <t>3444757</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3360575</t>
+          <t>3422538</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3401307</t>
+          <t>3463656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3616269</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3595393</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3634301</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7061026</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>7031109</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7084690</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3404826</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>2776876</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3608752</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>74,8%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8475</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6787888</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6118486</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6994982</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
